--- a/docs/EAA_So_sanh_Agent_nhung.xlsx
+++ b/docs/EAA_So_sanh_Agent_nhung.xlsx
@@ -12,12 +12,14 @@
     <sheet name="So tính năng" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Việc phải làm" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="EAA hơn ở đâu" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Kế hoạch vượt lên" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Nguồn khảo sát'!$A$1:$F$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'So tính năng'!$A$1:$J$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Việc phải làm'!$A$1:$E$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'EAA hơn ở đâu'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Kế hoạch vượt lên'!$A$1:$G$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4068,4 +4070,596 @@
   <autoFilter ref="A1:D7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Giai đoạn</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Việc</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Lấp mã</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Nuôi chiều sâu thế nào</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Chỗ đặt trong ba tầng</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>Mã TC</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Nặng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>GĐ1 · Bản đồ thanh ghi máy đọc được</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>GĐ1 · Bản đồ thanh ghi máy đọc được</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Bộ đọc CMSIS-SVD và ATDF về MỘT mô hình trung tính</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Cho `// ref:` một nguồn để đối chiếu — hôm nay cổng chỉ kiểm CÓ trích dẫn, không kiểm trích dẫn ĐÚNG</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>ENGINE eaa/regmap.py + regmap_svd.py + regmap_atdf.py (đọc ĐỊNH DẠNG, không biết tên thanh ghi nào); PACK khai đường dẫn; PROJECT giữ tệp</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>TC-136</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>vừa</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>GĐ1 · Bản đồ thanh ghi máy đọc được</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Cổng thứ năm `regcheck`: thanh ghi có thật, trường có thật, giá trị lọt vừa độ rộng, không ghi vào thanh ghi chỉ-đọc</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Chặn được hạng lỗi mà bốn cổng hiện tại không thấy: giá trị hợp cú pháp mà sai với silicon</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>ENGINE eaa/tools/regcheck.py, đứng sau `static` trước `unittests`</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>TC-136</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>vừa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>GĐ1 · Bản đồ thanh ghi máy đọc được</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Nối bản đồ vào N-908 và N-911</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>instrument.py biết giá trị mới có CÒN HỢP LỆ không, không chỉ biết nó đã đổi; dimension.py có nguồn thứ hai cho độ rộng và thang</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>ENGINE — sửa eaa/instrument.py và eaa/dimension.py</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>TC-137</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>nhẹ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>GĐ2 · Thước đo mới</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>GĐ2 · Thước đo mới</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Chỉ số của văn liệu: pass@1, pass@5, trượt dịch / sai hành vi / đúng</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>E1, E2</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Không có nó thì không đối thoại được với văn liệu. Dữ liệu đã có trong kpi_log.csv và llm_calls.jsonl — thiếu cách tính, không thiếu số</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>ENGINE eaa/bench.py; bộ nhiệm vụ nằm ở bench/&lt;bo&gt;/&lt;task&gt;/</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>TC-138</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>vừa</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>GĐ2 · Thước đo mới</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>BỐN TRỤC ĐO KHÔNG AI CÓ: độ nhạy bài kiểm · vá chỉnh đồ đo · mất việc im lặng · truy về được</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>E1, E2</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Đây là đóng góp nghiên cứu: không đua trên thước của họ mà đề xuất thước mới. Bốn bộ đo đã có sẵn (sensitivity, instrument, contract, regcheck)</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>ENGINE eaa/bench.py đọc kết quả của bốn module đã có</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>TC-138</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>vừa</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>GĐ3 · Kỹ năng phần cứng</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>GĐ3 · Kỹ năng phần cứng</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Kỹ năng theo ngoại vi: mẫu khởi tạo, THỨ TỰ bắt buộc, cách hỏng đã biết</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>B3, C8</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Chỗ DUY NHẤT bài arXiv đo được là nâng kết quả lên gần trần (41-42/42). Và nó chặn hạng lỗi đã làm robot ngã: mã đúng mọi dòng, sai ở THỨ TỰ</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>PACK packs/&lt;pack&gt;/skills/&lt;ngoại vi&gt;.md — tri thức của một họ chip, không phải của engine; ENGINE chỉ chọn theo `uses`</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>TC-139</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>vừa</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>GĐ3 · Kỹ năng phần cứng</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Lớp K9 trong bộ ghép prompt, chỉ nhận kỹ năng ĐÃ DUYỆT G2</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Bài arXiv đo được: kỹ năng LLM tự sinh cho lợi ích THẤT THƯỜNG. Cửa duyệt là chỗ chặn đúng điều ấy</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>ENGINE eaa/composer.py; ngân sách lấy từ `repair` (SÀN, không phải trần)</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>TC-139</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>nhẹ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>GĐ4 · Bối cảnh bo từ sơ đồ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>GĐ4 · Bối cảnh bo từ sơ đồ</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Đọc netlist KiCad → linh kiện, chân, net</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>hardware_profile.yaml gõ tay là chỗ SL-125 sai, và giá phải trả là robot lao thẳng một phía</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>ENGINE eaa/netlist.py (đọc ĐỊNH DẠNG mở); PROJECT giữ tệp</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>TC-140</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>nặng</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>GĐ4 · Bối cảnh bo từ sơ đồ</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>ĐỐI CHIẾU netlist với hồ sơ ở G1 — không sinh đè</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Hồ sơ mang thứ netlist không có: mức tích cực, pull-up nội, lý do chọn bộ đếm. Sinh đè là mất phần đắt nhất</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>ENGINE — lệch chân thì ĐỎ ở G1; linh kiện hồ sơ thiếu thì cảnh báo (ca SL-143: còi và nút có trên bo mà hồ sơ chưa bao giờ khai)</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>TC-140</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>vừa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Xen kẽ · rẻ, đáng làm, không nuôi chiều sâu</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Xen kẽ · rẻ, đáng làm, không nuôi chiều sâu</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Trọng tài phần cứng: khoá cổng nối tiếp</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Không nuôi chiều sâu, nhưng thành lỗi THẬT ngay khi có người thứ hai chạy cùng bo — nên làm sớm nhất trong ba</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>ENGINE eaa/serialport.py — một khoá tệp</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>TC-141</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>nhẹ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Xen kẽ · rẻ, đáng làm, không nuôi chiều sâu</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Truy vết hai chiều: tiêu chí nghiệm thu ↔ bài kiểm</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>ISO 26262 đòi yêu cầu ↔ mã ↔ kiểm chứng. EAA mạnh ở nhánh tri thức ↔ mã, chưa nối tiêu chí xuống từng bài kiểm</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>ENGINE eaa/acceptance.py + eaa/tools/unittests.py</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>TC-142</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>vừa</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Xen kẽ · rẻ, đáng làm, không nuôi chiều sâu</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Lớp mỏng tích hợp IDE</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Mặt tiếp xúc kỹ sư nhúng ngồi trong đó cả ngày. Không đụng lõi: gọi CLI</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>NGOÀI engine — một extension gọi `eaa` qua dòng lệnh</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>TC-143</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>vừa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Sau cùng · tốn thiết bị</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Sau cùng · tốn thiết bị</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Điều khiển máy đo, và phiên gỡ lỗi tự động</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>C5, C6</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Chỉ có nghĩa khi đã có benchmark để chứng minh chúng cải thiện được gì — tức là sau GĐ2</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>PACK khai tên máy đo và lệnh; ENGINE chỉ chuyển tiếp (đúng luật FR-PLT-01)</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>TC-144</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>nặng</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G20"/>
+  <mergeCells count="6">
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A19:G19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/EAA_So_sanh_Agent_nhung.xlsx
+++ b/docs/EAA_So_sanh_Agent_nhung.xlsx
@@ -17,8 +17,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Nguồn khảo sát'!$A$1:$F$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'So tính năng'!$A$1:$J$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Việc phải làm'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'EAA hơn ở đâu'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Việc phải làm'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'EAA hơn ở đâu'!$A$1:$D$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Kế hoạch vượt lên'!$A$1:$G$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1320,24 +1320,24 @@
           <t>không nêu</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
+          <t>eaa/regmap.py mô hình trung tính + regmap_svd.py + regmap_atdf.py; khai trong pack.yaml qua trường `regmap` · SL-176, TC-136</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>**EAA HƠN Ở PHẦN DÙNG NÓ.** Ngang về việc nạp; hơn ở chỗ cổng `regcheck` biến bản đồ thành bốn phép CHẶN (thanh ghi có thật · giá trị lọt vừa độ rộng · dịch bit trong tầm · không ghi vào thanh ghi chỉ-đọc) cộng một phép cảnh báo trích-dẫn-dán-nhầm-chỗ. Không nguồn nào khảo sát được nêu phép kiểm độ rộng trường bit</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>THIẾU RÕ. SVD là bảng thanh ghi máy đọc được, chính hãng phát hành — nó làm được đúng việc mà trích đoạn thủ công đang làm, nhanh hơn nhiều lần và ít sai hơn. Đây là khoảng trống đáng lấp nhất của nhóm A</t>
-        </is>
-      </c>
-      <c r="J4" s="16" t="inlineStr">
-        <is>
-          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Luật `// ref: &lt;mã chunk&gt;` cưỡng chế ở cổng phân tích tĩnh · TC-17</t>
+          <t>Luật `// ref: &lt;mã chunk&gt;` cưỡng chế ở cổng phân tích tĩnh · TC-17. Từ SL-176 thêm phép kiểm trích dẫn ĐÚNG CHỖ: hàm cấu hình thanh ghi X mà trích dẫn chunk không nói về X thì cảnh báo · TC-136</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -3476,7 +3476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Nạp SVD / file mô tả thanh ghi của hãng</t>
+          <t>Nạp SƠ ĐỒ NGUYÊN LÝ / netlist thành bối cảnh bo</t>
         </is>
       </c>
       <c r="D2" s="15" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>THIẾU RÕ. SVD là bảng thanh ghi máy đọc được, chính hãng phát hành — nó làm được đúng việc mà trích đoạn thủ công đang làm, nhanh hơn nhiều lần và ít sai hơn. Đây là khoảng trống đáng lấp nhất của nhóm A</t>
+          <t>THIẾU. Embedder khai đọc Altium/KiCad/Eagle/PADS/Xpedition rồi giải netlist ra chân, pull-up, địa chỉ bus. EAA nhận việc ấy bằng hardware_profile.yaml gõ tay — và SL-125 là lần chính chỗ gõ tay ấy sai</t>
         </is>
       </c>
     </row>
@@ -3548,22 +3548,22 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Nạp SƠ ĐỒ NGUYÊN LÝ / netlist thành bối cảnh bo</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+          <t>KỸ NĂNG chưng cất theo ngoại vi/MCU (mẫu + ràng buộc + cách hỏng)</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>THIẾU. Embedder khai đọc Altium/KiCad/Eagle/PADS/Xpedition rồi giải netlist ra chân, pull-up, địa chỉ bus. EAA nhận việc ấy bằng hardware_profile.yaml gõ tay — và SL-125 là lần chính chỗ gõ tay ấy sai</t>
+          <t>KHÁC HẠNG. `skills.py` của EAA rút kỹ năng QUY TRÌNH (chuỗi lệnh hay lặp); bài arXiv nói kỹ năng PHẦN CỨNG cho một ngoại vi — mẫu khởi tạo, thứ tự bắt buộc, cách hỏng đã biết. Và bài ấy ĐO được: kỹ năng do người soạn đạt 41-42/42, kỹ năng do LLM tự sinh thì lợi ích thất thường</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>KỸ NĂNG chưng cất theo ngoại vi/MCU (mẫu + ràng buộc + cách hỏng)</t>
+          <t>Benchmark có phần cứng THẬT, công bố được</t>
         </is>
       </c>
       <c r="D4" s="18" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>KHÁC HẠNG. `skills.py` của EAA rút kỹ năng QUY TRÌNH (chuỗi lệnh hay lặp); bài arXiv nói kỹ năng PHẦN CỨNG cho một ngoại vi — mẫu khởi tạo, thứ tự bắt buộc, cách hỏng đã biết. Và bài ấy ĐO được: kỹ năng do người soạn đạt 41-42/42, kỹ năng do LLM tự sinh thì lợi ích thất thường</t>
+          <t>KHOẢNG CÁCH RÕ. Bài arXiv có IoT-SkillsBench: 42 nhiệm vụ, 23 ngoại vi, 3 cặp nền tảng, 378 lượt chạy trên phần cứng thật, chỉ số CF/BF/BC và pass@1/pass@5. EAA có chiều SÂU trên một bài, chưa có chiều RỘNG</t>
         </is>
       </c>
     </row>
@@ -3602,49 +3602,49 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Benchmark có phần cứng THẬT, công bố được</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
+          <t>Chỉ số chuẩn: trượt dịch / sai hành vi / đúng, pass@k</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>THIẾU. Đây là ngôn ngữ mà người đọc luận văn dùng để so EAA với văn liệu. Rẻ: bộ dữ liệu đã có trong kpi_log, chỉ thiếu cách tính</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>Vừa</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Truy vấn tài liệu chính chủ lúc chạy (MCP / API hãng)</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>KHOẢNG CÁCH RÕ. Bài arXiv có IoT-SkillsBench: 42 nhiệm vụ, 23 ngoại vi, 3 cặp nền tảng, 378 lượt chạy trên phần cứng thật, chỉ số CF/BF/BC và pass@1/pass@5. EAA có chiều SÂU trên một bài, chưa có chiều RỘNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Cao</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Chỉ số chuẩn: trượt dịch / sai hành vi / đúng, pass@k</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>THIẾU. Đây là ngôn ngữ mà người đọc luận văn dùng để so EAA với văn liệu. Rẻ: bộ dữ liệu đã có trong kpi_log, chỉ thiếu cách tính</t>
+          <t>MỘT PHẦN. EAA tải được trang chính chủ và cưỡng chế hạng nguồn theo URL cuối — chỗ Espressif dùng MCP thì EAA dùng HTTP có kiểm hạng. Chưa nối máy chủ MCP nào của hãng</t>
         </is>
       </c>
     </row>
@@ -3656,12 +3656,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>B5</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Truy vấn tài liệu chính chủ lúc chạy (MCP / API hãng)</t>
+          <t>Bao phủ nhiều nền tảng / RTOS / SDK</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>MỘT PHẦN. EAA tải được trang chính chủ và cưỡng chế hạng nguồn theo URL cuối — chỗ Espressif dùng MCP thì EAA dùng HTTP có kiểm hạng. Chưa nối máy chủ MCP nào của hãng</t>
+          <t>Khoảng cách LỚN về BỀ RỘNG: Embedder khai 500+ nền tảng, 13 hãng, 5.500+ ngoại vi; bài arXiv có 3 cặp nền tảng–framework. EAA có 2 pack. Nhưng TC-47 đã chứng minh thêm pack không phải sửa engine — đây là công việc tuyến tính, không phải rào kiến trúc</t>
         </is>
       </c>
     </row>
@@ -3683,22 +3683,22 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>B5</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Bao phủ nhiều nền tảng / RTOS / SDK</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+          <t>Điều khiển máy đo: probe, logic analyzer, oscilloscope</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Khoảng cách LỚN về BỀ RỘNG: Embedder khai 500+ nền tảng, 13 hãng, 5.500+ ngoại vi; bài arXiv có 3 cặp nền tảng–framework. EAA có 2 pack. Nhưng TC-47 đã chứng minh thêm pack không phải sửa engine — đây là công việc tuyến tính, không phải rào kiến trúc</t>
+          <t>THIẾU. Embedder khai phối hợp 30+ probe và máy đo, phân tích dạng sóng, đo công suất tương quan với thực thi. Đây là khoảng cách phần cứng lớn nhất, và nó tốn tiền thiết bị chứ không chỉ tốn mã</t>
         </is>
       </c>
     </row>
@@ -3710,22 +3710,22 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Điều khiển máy đo: probe, logic analyzer, oscilloscope</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+          <t>Phiên gỡ lỗi qua debugger (đọc thanh ghi / bộ nhớ)</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>THIẾU. Embedder khai phối hợp 30+ probe và máy đo, phân tích dạng sóng, đo công suất tương quan với thực thi. Đây là khoảng cách phần cứng lớn nhất, và nó tốn tiền thiết bị chứ không chỉ tốn mã</t>
+          <t>MỘT PHẦN có chủ ý (T0). Nới lên T3 cần một mạch gỡ lỗi cắm vào bo thật, vốn ngoài phạm vi đề án — nhưng đây là chỗ đối thủ chạy tự động</t>
         </is>
       </c>
     </row>
@@ -3737,12 +3737,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Phiên gỡ lỗi qua debugger (đọc thanh ghi / bộ nhớ)</t>
+          <t>Sinh bài kiểm TỪ tài liệu phần cứng</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>MỘT PHẦN có chủ ý (T0). Nới lên T3 cần một mạch gỡ lỗi cắm vào bo thật, vốn ngoài phạm vi đề án — nhưng đây là chỗ đối thủ chạy tự động</t>
+          <t>MỘT PHẦN. Bài kiểm hiện sinh từ ý định module, không từ bảng thanh ghi. Sinh từ tài liệu là đường đi tới bài kiểm biết trước giá trị đúng</t>
         </is>
       </c>
     </row>
@@ -3764,22 +3764,22 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Sinh bài kiểm TỪ tài liệu phần cứng</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+          <t>Trọng tài phần cứng khi nhiều phiên dùng chung một bo</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>MỘT PHẦN. Bài kiểm hiện sinh từ ý định module, không từ bảng thanh ghi. Sinh từ tài liệu là đường đi tới bài kiểm biết trước giá trị đúng</t>
+          <t>THIẾU, và nó sẽ thành lỗi thật ngay khi có người thứ hai chạy cùng bo. Rẻ: một khoá tệp trên cổng nối tiếp</t>
         </is>
       </c>
     </row>
@@ -3791,22 +3791,22 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Trọng tài phần cứng khi nhiều phiên dùng chung một bo</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+          <t>Truy vết hai chiều yêu cầu ↔ mã ↔ kiểm chứng</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>THIẾU, và nó sẽ thành lỗi thật ngay khi có người thứ hai chạy cùng bo. Rẻ: một khoá tệp trên cổng nối tiếp</t>
+          <t>MỘT PHẦN. Chuẩn ISO 26262 đòi yêu cầu ↔ mã ↔ bài kiểm; EAA mạnh ở nhánh TRI THỨC ↔ mã nhưng chưa nối tiêu chí nghiệm thu xuống từng bài kiểm</t>
         </is>
       </c>
     </row>
@@ -3818,81 +3818,54 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Truy vết hai chiều yêu cầu ↔ mã ↔ kiểm chứng</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
+          <t>Tích hợp IDE (VS Code / Eclipse)</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>THIẾU. Đây là mặt tiếp xúc mà kỹ sư nhúng thật sự ngồi trong đó cả ngày. Không đụng tới lõi: một lớp mỏng gọi CLI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Chạy ngoại tuyến / trong mạng nội bộ / air-gapped</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN. Chuẩn ISO 26262 đòi yêu cầu ↔ mã ↔ bài kiểm; EAA mạnh ở nhánh TRI THỨC ↔ mã nhưng chưa nối tiêu chí nghiệm thu xuống từng bài kiểm</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Tích hợp IDE (VS Code / Eclipse)</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>THIẾU. Đây là mặt tiếp xúc mà kỹ sư nhúng thật sự ngồi trong đó cả ngày. Không đụng tới lõi: một lớp mỏng gọi CLI</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Chạy ngoại tuyến / trong mạng nội bộ / air-gapped</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
           <t>MỘT PHẦN: chạy được không mạng, nhưng lượt gọi mô hình THẬT vẫn đi ra API ngoài. Air-gapped đòi mô hình chạy tại chỗ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E15"/>
+  <autoFilter ref="A1:E14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3903,7 +3876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3937,137 +3910,159 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>Vòng đời tri thức: thay trích đoạn → truy ngược mã bị ảnh hưởng</t>
+          <t>Nạp SVD / file mô tả thanh ghi của hãng</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>eaa/lifecycle.py ba đường truy ngược + eaa knowledge stale · TC-29, TC-132</t>
+          <t>eaa/regmap.py mô hình trung tính + regmap_svd.py + regmap_atdf.py; khai trong pack.yaml qua trường `regmap` · SL-176, TC-136</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>**EAA HƠN.** Không nguồn nào trong khảo sát nêu năng lực này. Sửa một datasheet mà không biết mã nào đứng trên bản cũ là để lỗi nằm im</t>
+          <t>**EAA HƠN Ở PHẦN DÙNG NÓ.** Ngang về việc nạp; hơn ở chỗ cổng `regcheck` biến bản đồ thành bốn phép CHẶN (thanh ghi có thật · giá trị lọt vừa độ rộng · dịch bit trong tầm · không ghi vào thanh ghi chỉ-đọc) cộng một phép cảnh báo trích-dẫn-dán-nhầm-chỗ. Không nguồn nào khảo sát được nêu phép kiểm độ rộng trường bit</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Đo độ NHẠY của bài kiểm mới sinh</t>
+          <t>Vòng đời tri thức: thay trích đoạn → truy ngược mã bị ảnh hưởng</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>eaa/sensitivity.py chạy bộ kiểm mới trên mã vừa bị đánh đỏ · TC-128</t>
+          <t>eaa/lifecycle.py ba đường truy ngược + eaa knowledge stale · TC-29, TC-132</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>**EAA HƠN.** Không nguồn nào nêu. Một bài kiểm xanh chưa phải bằng chứng — và cả ba benchmark khảo sát được đều đo pass/fail chứ không hỏi bài kiểm ấy có phân biệt được gì không</t>
+          <t>**EAA HƠN.** Không nguồn nào trong khảo sát nêu năng lực này. Sửa một datasheet mà không biết mã nào đứng trên bản cũ là để lỗi nằm im</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>C11</t>
+          <t>C10</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Bắt mã TỰ CHỈNH cho vừa đồ đo của chính nó</t>
+          <t>Đo độ NHẠY của bài kiểm mới sinh</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>eaa/instrument.py ba dấu vết, dừng vòng vá và hỏi người · TC-131</t>
+          <t>eaa/sensitivity.py chạy bộ kiểm mới trên mã vừa bị đánh đỏ · TC-128</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>**EAA HƠN.** Đây là dạng hỏng qua sạch mọi cổng tự động — 3/12 lần từ chối G3 của chính đề án là nó. Không khảo sát nào nêu tới</t>
+          <t>**EAA HƠN.** Không nguồn nào nêu. Một bài kiểm xanh chưa phải bằng chứng — và cả ba benchmark khảo sát được đều đo pass/fail chứ không hỏi bài kiểm ấy có phân biệt được gì không</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>C12</t>
+          <t>C11</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Canh hợp đồng gọi và lời gọi bị đánh rơi giữa hai lượt sinh</t>
+          <t>Bắt mã TỰ CHỈNH cho vừa đồ đo của chính nó</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>eaa/contract.py chữ ký + tập lời gọi liên module · TC-124, TC-127</t>
+          <t>eaa/instrument.py ba dấu vết, dừng vòng vá và hỏi người · TC-131</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>**EAA HƠN.** Bằng chứng: `app_init()` mất bốn lời gọi khởi tạo, firmware câm, 33 bài kiểm vẫn xanh</t>
+          <t>**EAA HƠN.** Đây là dạng hỏng qua sạch mọi cổng tự động — 3/12 lần từ chối G3 của chính đề án là nó. Không khảo sát nào nêu tới</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>C12</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Tất định và tái lập được (điều kiện qualify công cụ)</t>
+          <t>Canh hợp đồng gọi và lời gọi bị đánh rơi giữa hai lượt sinh</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Ghim phiên bản model, prompt stateless, bộ phát lại từ nhật ký, env_lock băm toolchain · TC-11, TC-15, TC-36</t>
+          <t>eaa/contract.py chữ ký + tập lời gọi liên module · TC-124, TC-127</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>**EAA HƠN, và đây là điểm mạnh dễ bị bỏ qua nhất.** ISO 26262 đòi công cụ phân tích phải tất định mới qualify. Bộ phát lại cố ý KHÔNG bịa phản hồi khi trượt băm — một lượt phát lại tự sinh nội dung là bằng chứng giả</t>
+          <t>**EAA HƠN.** Bằng chứng: `app_init()` mất bốn lời gọi khởi tạo, firmware câm, 33 bài kiểm vẫn xanh</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Tất định và tái lập được (điều kiện qualify công cụ)</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Ghim phiên bản model, prompt stateless, bộ phát lại từ nhật ký, env_lock băm toolchain · TC-11, TC-15, TC-36</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>**EAA HƠN, và đây là điểm mạnh dễ bị bỏ qua nhất.** ISO 26262 đòi công cụ phân tích phải tất định mới qualify. Bộ phát lại cố ý KHÔNG bịa phản hồi khi trượt băm — một lượt phát lại tự sinh nội dung là bằng chứng giả</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
           <t>E6</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Sổ ghi mọi sai lệch giữa thiết kế và mã</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>docs/SAI_LECH_THIET_KE.md 175 mục + eaa/deviation.py + TC-60 quét mỗi lần chạy</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>**EAA HƠN.** Không nguồn nào nêu. Đây là dữ liệu gốc của phương pháp huấn luyện, và là thứ một sản phẩm thương mại không có lý do gì công bố</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/EAA_So_sanh_Agent_nhung.xlsx
+++ b/docs/EAA_So_sanh_Agent_nhung.xlsx
@@ -17,8 +17,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Nguồn khảo sát'!$A$1:$F$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'So tính năng'!$A$1:$J$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Việc phải làm'!$A$1:$E$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'EAA hơn ở đâu'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Việc phải làm'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'EAA hơn ở đâu'!$A$1:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Kế hoạch vượt lên'!$A$1:$G$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3012,24 +3012,24 @@
           <t>không nêu</t>
         </is>
       </c>
-      <c r="G40" s="15" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>kpi_log.csv đếm lượt gọi, vòng vá, quyết định gate — không có pass@k</t>
+          <t>eaa/bench.py: pass@k theo công thức không chệch của văn liệu + năm hạng (ba hạng chuẩn cộng HANDOFF và BLOCKED tách riêng) + lệnh eaa report bench · SL-177, TC-138</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>THIẾU. Đây là ngôn ngữ mà người đọc luận văn dùng để so EAA với văn liệu. Rẻ: bộ dữ liệu đã có trong kpi_log, chỉ thiếu cách tính</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>Cao</t>
+          <t>**EAA HƠN.** Ngang ở nửa thước của họ; hơn ở bốn trục đo CHẤT LƯỢNG QUÁ TRÌNH mà không benchmark nào trong khảo sát hỏi — độ nhạy bài kiểm, vá chỉnh đồ đo, mất việc im lặng, truy về được. Và nó không gộp kết quả trên bo với kết quả trên máy chủ thành một số</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3595,29 +3595,29 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>Cao</t>
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>Vừa</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Chỉ số chuẩn: trượt dịch / sai hành vi / đúng, pass@k</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+          <t>Truy vấn tài liệu chính chủ lúc chạy (MCP / API hãng)</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>THIẾU. Đây là ngôn ngữ mà người đọc luận văn dùng để so EAA với văn liệu. Rẻ: bộ dữ liệu đã có trong kpi_log, chỉ thiếu cách tính</t>
+          <t>MỘT PHẦN. EAA tải được trang chính chủ và cưỡng chế hạng nguồn theo URL cuối — chỗ Espressif dùng MCP thì EAA dùng HTTP có kiểm hạng. Chưa nối máy chủ MCP nào của hãng</t>
         </is>
       </c>
     </row>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>B5</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Truy vấn tài liệu chính chủ lúc chạy (MCP / API hãng)</t>
+          <t>Bao phủ nhiều nền tảng / RTOS / SDK</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>MỘT PHẦN. EAA tải được trang chính chủ và cưỡng chế hạng nguồn theo URL cuối — chỗ Espressif dùng MCP thì EAA dùng HTTP có kiểm hạng. Chưa nối máy chủ MCP nào của hãng</t>
+          <t>Khoảng cách LỚN về BỀ RỘNG: Embedder khai 500+ nền tảng, 13 hãng, 5.500+ ngoại vi; bài arXiv có 3 cặp nền tảng–framework. EAA có 2 pack. Nhưng TC-47 đã chứng minh thêm pack không phải sửa engine — đây là công việc tuyến tính, không phải rào kiến trúc</t>
         </is>
       </c>
     </row>
@@ -3656,22 +3656,22 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>B5</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Bao phủ nhiều nền tảng / RTOS / SDK</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+          <t>Điều khiển máy đo: probe, logic analyzer, oscilloscope</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Khoảng cách LỚN về BỀ RỘNG: Embedder khai 500+ nền tảng, 13 hãng, 5.500+ ngoại vi; bài arXiv có 3 cặp nền tảng–framework. EAA có 2 pack. Nhưng TC-47 đã chứng minh thêm pack không phải sửa engine — đây là công việc tuyến tính, không phải rào kiến trúc</t>
+          <t>THIẾU. Embedder khai phối hợp 30+ probe và máy đo, phân tích dạng sóng, đo công suất tương quan với thực thi. Đây là khoảng cách phần cứng lớn nhất, và nó tốn tiền thiết bị chứ không chỉ tốn mã</t>
         </is>
       </c>
     </row>
@@ -3683,22 +3683,22 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Điều khiển máy đo: probe, logic analyzer, oscilloscope</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+          <t>Phiên gỡ lỗi qua debugger (đọc thanh ghi / bộ nhớ)</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>THIẾU. Embedder khai phối hợp 30+ probe và máy đo, phân tích dạng sóng, đo công suất tương quan với thực thi. Đây là khoảng cách phần cứng lớn nhất, và nó tốn tiền thiết bị chứ không chỉ tốn mã</t>
+          <t>MỘT PHẦN có chủ ý (T0). Nới lên T3 cần một mạch gỡ lỗi cắm vào bo thật, vốn ngoài phạm vi đề án — nhưng đây là chỗ đối thủ chạy tự động</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Phiên gỡ lỗi qua debugger (đọc thanh ghi / bộ nhớ)</t>
+          <t>Sinh bài kiểm TỪ tài liệu phần cứng</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>MỘT PHẦN có chủ ý (T0). Nới lên T3 cần một mạch gỡ lỗi cắm vào bo thật, vốn ngoài phạm vi đề án — nhưng đây là chỗ đối thủ chạy tự động</t>
+          <t>MỘT PHẦN. Bài kiểm hiện sinh từ ý định module, không từ bảng thanh ghi. Sinh từ tài liệu là đường đi tới bài kiểm biết trước giá trị đúng</t>
         </is>
       </c>
     </row>
@@ -3737,22 +3737,22 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Sinh bài kiểm TỪ tài liệu phần cứng</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+          <t>Trọng tài phần cứng khi nhiều phiên dùng chung một bo</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>MỘT PHẦN. Bài kiểm hiện sinh từ ý định module, không từ bảng thanh ghi. Sinh từ tài liệu là đường đi tới bài kiểm biết trước giá trị đúng</t>
+          <t>THIẾU, và nó sẽ thành lỗi thật ngay khi có người thứ hai chạy cùng bo. Rẻ: một khoá tệp trên cổng nối tiếp</t>
         </is>
       </c>
     </row>
@@ -3764,22 +3764,22 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Trọng tài phần cứng khi nhiều phiên dùng chung một bo</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+          <t>Truy vết hai chiều yêu cầu ↔ mã ↔ kiểm chứng</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>THIẾU, và nó sẽ thành lỗi thật ngay khi có người thứ hai chạy cùng bo. Rẻ: một khoá tệp trên cổng nối tiếp</t>
+          <t>MỘT PHẦN. Chuẩn ISO 26262 đòi yêu cầu ↔ mã ↔ bài kiểm; EAA mạnh ở nhánh TRI THỨC ↔ mã nhưng chưa nối tiêu chí nghiệm thu xuống từng bài kiểm</t>
         </is>
       </c>
     </row>
@@ -3791,81 +3791,54 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Truy vết hai chiều yêu cầu ↔ mã ↔ kiểm chứng</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
+          <t>Tích hợp IDE (VS Code / Eclipse)</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>THIẾU. Đây là mặt tiếp xúc mà kỹ sư nhúng thật sự ngồi trong đó cả ngày. Không đụng tới lõi: một lớp mỏng gọi CLI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Chạy ngoại tuyến / trong mạng nội bộ / air-gapped</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN. Chuẩn ISO 26262 đòi yêu cầu ↔ mã ↔ bài kiểm; EAA mạnh ở nhánh TRI THỨC ↔ mã nhưng chưa nối tiêu chí nghiệm thu xuống từng bài kiểm</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Tích hợp IDE (VS Code / Eclipse)</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>THIẾU. Đây là mặt tiếp xúc mà kỹ sư nhúng thật sự ngồi trong đó cả ngày. Không đụng tới lõi: một lớp mỏng gọi CLI</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Chạy ngoại tuyến / trong mạng nội bộ / air-gapped</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
           <t>MỘT PHẦN: chạy được không mạng, nhưng lượt gọi mô hình THẬT vẫn đi ra API ngoài. Air-gapped đòi mô hình chạy tại chỗ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E14"/>
+  <autoFilter ref="A1:E13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3876,7 +3849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4020,49 +3993,71 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Tất định và tái lập được (điều kiện qualify công cụ)</t>
+          <t>Chỉ số chuẩn: trượt dịch / sai hành vi / đúng, pass@k</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Ghim phiên bản model, prompt stateless, bộ phát lại từ nhật ký, env_lock băm toolchain · TC-11, TC-15, TC-36</t>
+          <t>eaa/bench.py: pass@k theo công thức không chệch của văn liệu + năm hạng (ba hạng chuẩn cộng HANDOFF và BLOCKED tách riêng) + lệnh eaa report bench · SL-177, TC-138</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>**EAA HƠN, và đây là điểm mạnh dễ bị bỏ qua nhất.** ISO 26262 đòi công cụ phân tích phải tất định mới qualify. Bộ phát lại cố ý KHÔNG bịa phản hồi khi trượt băm — một lượt phát lại tự sinh nội dung là bằng chứng giả</t>
+          <t>**EAA HƠN.** Ngang ở nửa thước của họ; hơn ở bốn trục đo CHẤT LƯỢNG QUÁ TRÌNH mà không benchmark nào trong khảo sát hỏi — độ nhạy bài kiểm, vá chỉnh đồ đo, mất việc im lặng, truy về được. Và nó không gộp kết quả trên bo với kết quả trên máy chủ thành một số</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Tất định và tái lập được (điều kiện qualify công cụ)</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Ghim phiên bản model, prompt stateless, bộ phát lại từ nhật ký, env_lock băm toolchain · TC-11, TC-15, TC-36</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>**EAA HƠN, và đây là điểm mạnh dễ bị bỏ qua nhất.** ISO 26262 đòi công cụ phân tích phải tất định mới qualify. Bộ phát lại cố ý KHÔNG bịa phản hồi khi trượt băm — một lượt phát lại tự sinh nội dung là bằng chứng giả</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
           <t>E6</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Sổ ghi mọi sai lệch giữa thiết kế và mã</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>docs/SAI_LECH_THIET_KE.md 175 mục + eaa/deviation.py + TC-60 quét mỗi lần chạy</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>**EAA HƠN.** Không nguồn nào nêu. Đây là dữ liệu gốc của phương pháp huấn luyện, và là thứ một sản phẩm thương mại không có lý do gì công bố</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D8"/>
+  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
